--- a/01_analyses_states/Uttar Pradesh/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Uttar Pradesh/results/SoIB_summaries.xlsx
@@ -396,13 +396,13 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2">
         <v>6.7</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="3">
@@ -412,16 +412,16 @@
         </is>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D3">
-        <v>6.7</v>
+        <v>13.3</v>
       </c>
       <c r="E3">
-        <v>21.6</v>
+        <v>23.3</v>
       </c>
     </row>
     <row r="4">
@@ -431,16 +431,16 @@
         </is>
       </c>
       <c r="B4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C4">
         <v>23</v>
       </c>
       <c r="D4">
-        <v>26.7</v>
+        <v>20</v>
       </c>
       <c r="E4">
-        <v>62.2</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="5">
@@ -450,16 +450,16 @@
         </is>
       </c>
       <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
         <v>6</v>
       </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
       <c r="D5">
-        <v>40</v>
+        <v>33.3</v>
       </c>
       <c r="E5">
-        <v>10.8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
@@ -469,16 +469,16 @@
         </is>
       </c>
       <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
         <v>3</v>
       </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
       <c r="D6">
-        <v>20</v>
+        <v>26.7</v>
       </c>
       <c r="E6">
-        <v>5.4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -491,7 +491,7 @@
         <v>9</v>
       </c>
       <c r="C7">
-        <v>73</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8">
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C8">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
   </sheetData>
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
   </sheetData>
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="3">
@@ -706,7 +706,7 @@
         <v>110</v>
       </c>
       <c r="C4">
-        <v>37</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5">

--- a/01_analyses_states/Uttar Pradesh/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Uttar Pradesh/results/SoIB_summaries.xlsx
@@ -396,13 +396,13 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2">
         <v>6.7</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="3">
@@ -412,16 +412,16 @@
         </is>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3">
         <v>10</v>
       </c>
       <c r="D3">
-        <v>6.7</v>
+        <v>13.3</v>
       </c>
       <c r="E3">
-        <v>22.2</v>
+        <v>23.3</v>
       </c>
     </row>
     <row r="4">
@@ -431,16 +431,16 @@
         </is>
       </c>
       <c r="B4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D4">
-        <v>26.7</v>
+        <v>20</v>
       </c>
       <c r="E4">
-        <v>60</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="5">
@@ -450,16 +450,16 @@
         </is>
       </c>
       <c r="B5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C5">
         <v>6</v>
       </c>
       <c r="D5">
-        <v>40</v>
+        <v>33.3</v>
       </c>
       <c r="E5">
-        <v>13.3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
@@ -469,16 +469,16 @@
         </is>
       </c>
       <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
         <v>3</v>
       </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
       <c r="D6">
-        <v>20</v>
+        <v>26.7</v>
       </c>
       <c r="E6">
-        <v>4.4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -491,7 +491,7 @@
         <v>9</v>
       </c>
       <c r="C7">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8">
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C8">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
   </sheetData>
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
   </sheetData>
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="3">
@@ -706,7 +706,7 @@
         <v>110</v>
       </c>
       <c r="C4">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5">

--- a/01_analyses_states/Uttar Pradesh/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Uttar Pradesh/results/SoIB_summaries.xlsx
@@ -393,16 +393,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>6.7</v>
+        <v>18.2</v>
       </c>
       <c r="E2">
-        <v>2.3</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="3">
@@ -415,13 +415,13 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D3">
-        <v>13.3</v>
+        <v>18.2</v>
       </c>
       <c r="E3">
-        <v>23.3</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="4">
@@ -431,16 +431,16 @@
         </is>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D4">
-        <v>20</v>
+        <v>36.4</v>
       </c>
       <c r="E4">
-        <v>53.5</v>
+        <v>70.59999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -450,16 +450,16 @@
         </is>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D5">
-        <v>33.3</v>
+        <v>9.1</v>
       </c>
       <c r="E5">
-        <v>14</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="6">
@@ -469,16 +469,16 @@
         </is>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>26.7</v>
+        <v>18.2</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="7">
@@ -488,10 +488,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C7">
-        <v>67</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8">
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="C8">
-        <v>348</v>
+        <v>343</v>
       </c>
     </row>
   </sheetData>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>286</v>
+        <v>387</v>
       </c>
     </row>
     <row r="4">
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>553</v>
+        <v>441</v>
       </c>
     </row>
   </sheetData>
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>458</v>
+        <v>451</v>
       </c>
     </row>
     <row r="3">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C3">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C4">
-        <v>43</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5">
@@ -763,16 +763,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E2">
-        <v>76.09999999999999</v>
+        <v>73.90000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -782,16 +782,16 @@
         </is>
       </c>
       <c r="B3">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C3">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D3">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E3">
-        <v>23.9</v>
+        <v>26.1</v>
       </c>
     </row>
   </sheetData>
